--- a/results/job_matches_2026-10-02.xlsx
+++ b/results/job_matches_2026-10-02.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Match Score (%)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Matched Keywords</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Posted At</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Apply Link</t>
         </is>
@@ -468,60 +456,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr Data Engineer (Data Quality &amp; Data Governance)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IAM, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Oozie, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93507bcf9f653a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d0e854dcd2654c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>AWS Lakehouse Data Engineer- GrantSolutions experienced only</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bda7c67bf5cbe5a</t>
+          <t>https://www.indeed.com/viewjob?jk=16509765dca147b7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Shelton - Data Engineering - Engr- Data II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +554,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368616de2c642a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=92ef615c91382283</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Financial Services Technology Consulting, Financial Risk Technology (FRT) Engineering - Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Event Hubs, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2c64c083ac8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8d4e445d09c33470</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576d7762bdc9b4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=24dadced559e6fd5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Data Architect - Associate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22.2</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b81bea3b93bc1223</t>
+          <t>https://www.indeed.com/viewjob?jk=8052dec6a7c72b4e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>AI Enterprise Architect-3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22.2</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2999a5d3b3483e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f935ebfaf4a8e1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.2</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bb2920db804ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=712c0b25aa3285b3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eda93b383c5e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d212983a598443</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Promevo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>IAM, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059b0e91bd7ff509</t>
+          <t>https://www.indeed.com/viewjob?jk=bf209f051368f0a6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Senior Full Stack Java Developer – Cloud &amp; Microservices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce8f2606e05ad08</t>
+          <t>https://www.indeed.com/viewjob?jk=32694f181dd53cec</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Senior Full Stack Java Developer – Cloud &amp; Microservices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +869,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec1f17f9b315e61</t>
+          <t>https://www.indeed.com/viewjob?jk=732a103772c5609a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,11 +890,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +904,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=800aea21a1783ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=370116783b30ec82</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -937,11 +925,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +939,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f5b12bfd4b6b93</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08e1ab394481f7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -972,11 +960,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +974,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc68cc09e742d8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=05a68983fb26d208</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,11 +995,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1009,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4c45e6b0b429cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3d2eb1b1d44236b5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1030,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1044,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43630d97f73e088d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7ec08cb54132eb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1077,11 +1065,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1079,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9ae51cfd68f91d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3dca3caa8fcea29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,11 +1100,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1114,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1f9238d3e58cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d25b4abde31c27c6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1135,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1149,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99194701eec56644</t>
+          <t>https://www.indeed.com/viewjob?jk=6b100a75517534d8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,11 +1170,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1184,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b18fb0f3a526243</t>
+          <t>https://www.indeed.com/viewjob?jk=07dbaef7d4e6b9c5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1205,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1219,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d368a77fc60527a</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f2bc46540393f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,11 +1240,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1254,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1833b1fd89a44d</t>
+          <t>https://www.indeed.com/viewjob?jk=9307d6216e415e2b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1275,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1289,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7543f28ff561431d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e546f6d2550b6b2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1310,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1324,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c42affa850495e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9cc3a9842afff5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1345,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1359,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3cc93c9c31df31</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d753c3c316503b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1392,11 +1380,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1394,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b66559440a56821</t>
+          <t>https://www.indeed.com/viewjob?jk=a584ad2f7d15ff00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,11 +1415,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1429,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681075eb2dbba34a</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb65440d87333c8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,11 +1450,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1464,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acaf7efa66ec3e91</t>
+          <t>https://www.indeed.com/viewjob?jk=f11b515a70c088cb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1497,11 +1485,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1499,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd121f5727f4582b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e6bf2001d3580b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1532,11 +1520,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1534,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593df49c1a783823</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5e5c4e23854a04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1567,11 +1555,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1569,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c701c0131a9463b2</t>
+          <t>https://www.indeed.com/viewjob?jk=32200d4c67603056</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1602,11 +1590,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1604,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2153f02dbc5939c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e7bd83f43b5bd8e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1637,11 +1625,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1639,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f50184907f6d74c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6a5d892b0aabd5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1672,11 +1660,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1674,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc904f2cbbfb0652</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbff2b8b357f56c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1707,11 +1695,11 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1709,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24738a39909ebdb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b86ae33f22adc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1742,11 +1730,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1744,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4e5cf428179e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=722290f8547af1ca</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Engineer (Data Quality &amp; Data Governance)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1779,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d0e854dcd2654c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f098ed101bfb827</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Lakehouse Data Engineer- GrantSolutions experienced only</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1814,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16509765dca147b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c34c424587e49ee0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Shelton - Data Engineering - Engr- Data II</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1849,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ef615c91382283</t>
+          <t>https://www.indeed.com/viewjob?jk=71f963121f68d02a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Predictive Maintenance</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AssetWatch</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Timestream, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1884,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a533bcbf8ae0b71</t>
+          <t>https://www.indeed.com/viewjob?jk=4854ae8a484d616d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Financial Services Technology Consulting, Financial Risk Technology (FRT) Engineering - Senior</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Event Hubs, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d4e445d09c33470</t>
+          <t>https://www.indeed.com/viewjob?jk=65206dd20456c905</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1954,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24dadced559e6fd5</t>
+          <t>https://www.indeed.com/viewjob?jk=88b74e153a8fefec</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect - Associate</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>West Valley City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +1989,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8052dec6a7c72b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=02838770465f88cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect-3</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f935ebfaf4a8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=77cd65e0f3142719</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Microservices Digital Software Engineer (Citi Retail Services)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5706dd6baebfde8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a12237447e502074</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d212983a598443</t>
+          <t>https://www.indeed.com/viewjob?jk=2f15fa276e024e09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Promevo</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2129,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf209f051368f0a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c916f7f491c0fd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2164,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370116783b30ec82</t>
+          <t>https://www.indeed.com/viewjob?jk=e6507575b2b0bc68</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2199,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08e1ab394481f7</t>
+          <t>https://www.indeed.com/viewjob?jk=4b664305c66c3760</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2234,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a68983fb26d208</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2c17b6e6619517</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Spark, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d2eb1b1d44236b5</t>
+          <t>https://www.indeed.com/viewjob?jk=9b838b29c7c8ad8f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer (Contract-To-Hire) (Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>RelMap Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2304,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7ec08cb54132eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f168390c3d4033ba</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2339,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3dca3caa8fcea29</t>
+          <t>https://www.indeed.com/viewjob?jk=f13d4667a77f2594</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2374,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25b4abde31c27c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7337e87916fb1c2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>.NET API Solutions Architect on W2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2409,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b100a75517534d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1014dc90e0bbcda2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Pillsbury Winthrop Shaw Pittman</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2444,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dbaef7d4e6b9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4506845d5307539</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2479,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f2bc46540393f</t>
+          <t>https://www.indeed.com/viewjob?jk=45753ce4c6ce5c87</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>ML Engineer- Sr Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2512,11 +2500,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>RDS, Databricks, Vertex AI, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2514,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9307d6216e415e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cdc87ac9c054fa1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>ETL Engineer – Cloud Data Lakehouse &amp; Pipeline Development</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Hays Electrical Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2549,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e546f6d2550b6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fca3c9a5cdbe11b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer | Talent Community</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2584,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9cc3a9842afff5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6682604b8f254c7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer - Java Microservices &amp; AWS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d753c3c316503b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff68c4379d27e34</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>RS&amp;H</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Scala, Polars, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2654,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a584ad2f7d15ff00</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b809a99c4ae691</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior OCI Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2689,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb65440d87333c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6ff336981b55a2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2724,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11b515a70c088cb</t>
+          <t>https://www.indeed.com/viewjob?jk=597b472661d238bf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2759,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e6bf2001d3580b</t>
+          <t>https://www.indeed.com/viewjob?jk=54993a3d0229e1bd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>FCCI Insurance Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2794,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5e5c4e23854a04</t>
+          <t>https://www.indeed.com/viewjob?jk=0cf8e2097b223c45</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2829,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32200d4c67603056</t>
+          <t>https://www.indeed.com/viewjob?jk=3b988244eb4ead63</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>SPEC SOFTWARE DEVT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2864,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e7bd83f43b5bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0443de525123e0a5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Sr. Clinical Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2899,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6a5d892b0aabd5</t>
+          <t>https://www.indeed.com/viewjob?jk=17f0d739bf16af91</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>ML Ops Engineer I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Murphy USA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>El Dorado, AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2934,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbff2b8b357f56c</t>
+          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,19 +2969,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b86ae33f22adc</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f8125afe117b73</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3002,11 +2990,11 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3004,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722290f8547af1ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbb1a0c9f6d5c59</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer-2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f098ed101bfb827</t>
+          <t>https://www.indeed.com/viewjob?jk=40bc48c467a02cd0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Talsolution</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3074,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34c424587e49ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d10ea1903db7019</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Backend Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Azure, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3109,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f963121f68d02a</t>
+          <t>https://www.indeed.com/viewjob?jk=8672fb0f9146fe17</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Software Engineer III - ML Model Delivery</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3144,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4854ae8a484d616d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9623715fec95146</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, S3, ECS, IAM, RDS, Vertex AI, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3179,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65206dd20456c905</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3214,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b74e153a8fefec</t>
+          <t>https://www.indeed.com/viewjob?jk=d842e057aeca5cf9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>FBS Senior Data Engineer (SnowFlake)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Farmers Insurance Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3249,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02838770465f88cb</t>
+          <t>https://www.indeed.com/viewjob?jk=740eac621cae0ece</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>ChenMed</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3284,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cd65e0f3142719</t>
+          <t>https://www.indeed.com/viewjob?jk=05e9d9a6218bf629</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3319,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12237447e502074</t>
+          <t>https://www.indeed.com/viewjob?jk=a0058b8ece0bab0e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3354,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f15fa276e024e09</t>
+          <t>https://www.indeed.com/viewjob?jk=fce0252be99bd916</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3389,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c916f7f491c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d0afa695590a0c66</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer – Cloud &amp; Microservices</t>
+          <t>Associate Data Engineer - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3424,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32694f181dd53cec</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e9b66a0edb57d7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer – Cloud &amp; Microservices</t>
+          <t>Associate Data Engineer - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3459,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=732a103772c5609a</t>
+          <t>https://www.indeed.com/viewjob?jk=900e2c37f8055534</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3494,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6507575b2b0bc68</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0c66ac5431d7f0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Reporting</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JustPark</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, GCP, BigQuery, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3529,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b664305c66c3760</t>
+          <t>https://www.indeed.com/viewjob?jk=d9067ce361a1da61</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3564,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2c17b6e6619517</t>
+          <t>https://www.indeed.com/viewjob?jk=e6429def610f5341</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Spark, Kafka</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3599,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b838b29c7c8ad8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-To-Hire) (Remote)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RelMap Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3634,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f168390c3d4033ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d39184c61f9a086c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3669,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f13d4667a77f2594</t>
+          <t>https://www.indeed.com/viewjob?jk=79f48860ff6de64c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,172 +3704,172 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7337e87916fb1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=22ff23a516389c02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Analytics Engineer (Data Platform &amp; AI Enablement)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eab9d45a7707f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=c028808e0e50f38b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineering &amp; BI/Analytics</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Advancio</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Downey, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab75b27388163f6</t>
+          <t>https://www.indeed.com/viewjob?jk=30859e3f8aec8e8c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Department of Motor Vehicles California</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9f207b6755f4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd56cb6c6641f35</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>.NET API Solutions Architect on W2</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1014dc90e0bbcda2</t>
+          <t>https://www.indeed.com/viewjob?jk=b862a52465289faa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Full-Stack Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pillsbury Winthrop Shaw Pittman</t>
+          <t>Abacus Technology</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Data Modeling, ELT, MLflow, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,102 +3879,102 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4506845d5307539</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d8b03546e93eeb</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53e345da3563756</t>
+          <t>https://www.indeed.com/viewjob?jk=35397f2df8eceb18</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Azure Data Engineer Senior</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc8b1810e1fdd4c8</t>
+          <t>https://www.indeed.com/viewjob?jk=35a87a481b03a8f0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ETL Engineer – Cloud Data Lakehouse &amp; Pipeline Development</t>
+          <t>Junior Azure Data Engineer - UniFirst</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hays Electrical Services</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>14.6</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3984,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fca3c9a5cdbe11b</t>
+          <t>https://www.indeed.com/viewjob?jk=c44239a8e09ed622</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data (L3)</t>
+          <t>IT Data Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>GCI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>14.6</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4019,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102cee0c6adcda4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f42d08c79858e06</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior OCI Consultant</t>
+          <t>Junior Azure Data Engineer - UniFirst</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>14.6</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4054,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6ff336981b55a2</t>
+          <t>https://www.indeed.com/viewjob?jk=24ec3bf6a35a904c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend Services</t>
+          <t>Senior Specialist, Manufacturing Data Engineering &amp; Digital Integration</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>14.6</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4089,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e3a4fbe236b819</t>
+          <t>https://www.indeed.com/viewjob?jk=082180c5e373ebfd</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4124,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597b472661d238bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d75297369fa64ca</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ML Engineer- Sr Consultant</t>
+          <t>Data Engineer – Azure</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Symphony Enterprises Llc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Vertex AI, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4159,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cdc87ac9c054fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b8c1c6cf55d819e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>AI and Software Solutions Architect (Remote, Contract)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>INFUSE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4194,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54993a3d0229e1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bfa1f3245af737</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Power BI / SQL Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FCCI Insurance Group</t>
+          <t>The Data Element</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4229,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf8e2097b223c45</t>
+          <t>https://www.indeed.com/viewjob?jk=9e924fcba2ecc0fc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SPEC SOFTWARE DEVT</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4264,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0443de525123e0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Clinical Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, ETL, ELT</t>
+          <t>AWS, Athena, Step Functions, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,1722 +4299,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f0d739bf16af91</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>ML Ops Engineer I</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Murphy USA</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>El Dorado, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Jr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>NAVA TECH LLC</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbb1a0c9f6d5c59</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Data Engineer-2</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40bc48c467a02cd0</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Talsolution</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d10ea1903db7019</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d01528e1099d2199</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Adonis</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, IAM, RDS, Scala, Snowflake, DynamoDB, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0454d0d787afaef</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (SQL, AWS, &amp; Java)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>INTRAFI</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, Data Modeling, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93b33418deacae1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>SRE - DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, Scala, Power BI, Splunk, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c99c9c660d572e7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Solventum</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, ETL, dbt, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c4e4827f2acca3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer 2</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>KONG</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d842e057aeca5cf9</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Arrowstreet Capital LP</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e50557e995a6e35f</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Lam Research</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37649d4b62a2de47</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer - ED&amp;A - Global Industrial</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Motion</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, BigQuery, Cloud Storage, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=006bd2455950a26a</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Software Engineer III - ML Model Delivery</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9623715fec95146</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Data Solution Architect</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Madison, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0058b8ece0bab0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Data Solution Architect</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fce0252be99bd916</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Solution Architect</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Baker Tilly Canada</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0afa695590a0c66</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Associate Data Engineer - Onsite Hybrid</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e9b66a0edb57d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Associate Data Engineer - Onsite Hybrid</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=900e2c37f8055534</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0c66ac5431d7f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Platform Application Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>A-V SERVICES INC.</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9985441c9238ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Software Engineer – SaaS &amp; Data Migration Specialist</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Solen Software Group</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, ECS, Azure, GCP, Scala, SQL Server, DataOps, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e93b4193751c0db</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II, Ads Data Solutions Engineering</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, dbt, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb84207463f6a555</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Reporting</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>JustPark</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, GCP, BigQuery, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9067ce361a1da61</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Palantir Foundry Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Kosma Tech Inc</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Kafka, ETL, ELT, Terraform</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d62cd65b081a5fd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6429def610f5341</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Analytics Data Engineer II - Homes.com - Arlington, VA</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>CoStar Group</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=196fad23ac814fb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>GreenStone Farm Credit Services</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>East Lansing, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8fa8b2a51a2522</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79f48860ff6de64c</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22ff23a516389c02</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Growth Acquisition (Growth &amp; Marketing Data)</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a131fa3a50c5d619</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer (Data Platform &amp; AI Enablement)</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Delta Faucet Company</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c028808e0e50f38b</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Plante Moran</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35a87a481b03a8f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Exostar</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35397f2df8eceb18</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer 4 (Python, Java, AWS)</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa0a61b0b1456bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c87481ab8ef4260</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Junior Azure Data Engineer - UniFirst</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ec3bf6a35a904c</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d75297369fa64ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Data Engineer with Healthcare Data Platforms</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89c3715c2c5b9b53</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Data Engineer – Azure</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Symphony Enterprises Llc</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b8c1c6cf55d819e</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f98b7445f4c23e54</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer I</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>AmeriHealth Caritas</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c15de344a8583c9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>AI and Software Solutions Architect (Remote, Contract)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>INFUSE</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bfa1f3245af737</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Senior Power BI / SQL Developer</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>The Data Element</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e924fcba2ecc0fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Flexera</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, Athena, Step Functions, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=baa8123cd97b3b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Sr. Business Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Engineering Applications</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f46dbaea5d78f85</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Engineer IV, ECM Developer</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>X-Energy</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=992ec04c34232f03</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-02.xlsx
+++ b/results/job_matches_2026-10-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,12 +736,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Promevo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>IAM, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,19 +764,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d212983a598443</t>
+          <t>https://www.indeed.com/viewjob?jk=bf209f051368f0a6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Promevo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf209f051368f0a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d212983a598443</t>
         </is>
       </c>
     </row>
@@ -841,17 +841,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer – Cloud &amp; Microservices</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=732a103772c5609a</t>
+          <t>https://www.indeed.com/viewjob?jk=370116783b30ec82</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370116783b30ec82</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08e1ab394481f7</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08e1ab394481f7</t>
+          <t>https://www.indeed.com/viewjob?jk=05a68983fb26d208</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a68983fb26d208</t>
+          <t>https://www.indeed.com/viewjob?jk=3d2eb1b1d44236b5</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d2eb1b1d44236b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7ec08cb54132eb</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7ec08cb54132eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3dca3caa8fcea29</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3dca3caa8fcea29</t>
+          <t>https://www.indeed.com/viewjob?jk=d25b4abde31c27c6</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25b4abde31c27c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b100a75517534d8</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b100a75517534d8</t>
+          <t>https://www.indeed.com/viewjob?jk=07dbaef7d4e6b9c5</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dbaef7d4e6b9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f2bc46540393f</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f2bc46540393f</t>
+          <t>https://www.indeed.com/viewjob?jk=9307d6216e415e2b</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9307d6216e415e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e546f6d2550b6b2</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e546f6d2550b6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9cc3a9842afff5</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9cc3a9842afff5</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d753c3c316503b</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d753c3c316503b</t>
+          <t>https://www.indeed.com/viewjob?jk=a584ad2f7d15ff00</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a584ad2f7d15ff00</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb65440d87333c8</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb65440d87333c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f11b515a70c088cb</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11b515a70c088cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e6bf2001d3580b</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e6bf2001d3580b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5e5c4e23854a04</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5e5c4e23854a04</t>
+          <t>https://www.indeed.com/viewjob?jk=32200d4c67603056</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32200d4c67603056</t>
+          <t>https://www.indeed.com/viewjob?jk=9e7bd83f43b5bd8e</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e7bd83f43b5bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6a5d892b0aabd5</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6a5d892b0aabd5</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbff2b8b357f56c</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbff2b8b357f56c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b86ae33f22adc</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b86ae33f22adc</t>
+          <t>https://www.indeed.com/viewjob?jk=722290f8547af1ca</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722290f8547af1ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5f098ed101bfb827</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f098ed101bfb827</t>
+          <t>https://www.indeed.com/viewjob?jk=c34c424587e49ee0</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34c424587e49ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=71f963121f68d02a</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f963121f68d02a</t>
+          <t>https://www.indeed.com/viewjob?jk=4854ae8a484d616d</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4854ae8a484d616d</t>
+          <t>https://www.indeed.com/viewjob?jk=65206dd20456c905</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65206dd20456c905</t>
+          <t>https://www.indeed.com/viewjob?jk=88b74e153a8fefec</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b74e153a8fefec</t>
+          <t>https://www.indeed.com/viewjob?jk=02838770465f88cb</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02838770465f88cb</t>
+          <t>https://www.indeed.com/viewjob?jk=77cd65e0f3142719</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cd65e0f3142719</t>
+          <t>https://www.indeed.com/viewjob?jk=a12237447e502074</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12237447e502074</t>
+          <t>https://www.indeed.com/viewjob?jk=2f15fa276e024e09</t>
         </is>
       </c>
     </row>
@@ -2094,32 +2094,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f15fa276e024e09</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c916f7f491c0fd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer (Contract-To-Hire) (Remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>RelMap Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c916f7f491c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f168390c3d4033ba</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,19 +2164,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6507575b2b0bc68</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2c17b6e6619517</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Spark, Kafka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,32 +2199,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b664305c66c3760</t>
+          <t>https://www.indeed.com/viewjob?jk=9b838b29c7c8ad8f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,32 +2234,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2c17b6e6619517</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c381b09f7b36b3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b838b29c7c8ad8f</t>
+          <t>https://www.indeed.com/viewjob?jk=f13d4667a77f2594</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-To-Hire) (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RelMap Consulting</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f168390c3d4033ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a7337e87916fb1c2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>.NET API Solutions Architect on W2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f13d4667a77f2594</t>
+          <t>https://www.indeed.com/viewjob?jk=1014dc90e0bbcda2</t>
         </is>
       </c>
     </row>
@@ -2351,20 +2351,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,32 +2374,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7337e87916fb1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=45753ce4c6ce5c87</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>.NET API Solutions Architect on W2</t>
+          <t>ETL Engineer – Cloud Data Lakehouse &amp; Pipeline Development</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Hays Electrical Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,32 +2409,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1014dc90e0bbcda2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fca3c9a5cdbe11b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer | Talent Community</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pillsbury Winthrop Shaw Pittman</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,32 +2444,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4506845d5307539</t>
+          <t>https://www.indeed.com/viewjob?jk=b6682604b8f254c7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Engineer- Sr Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Vertex AI, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45753ce4c6ce5c87</t>
+          <t>https://www.indeed.com/viewjob?jk=1cdc87ac9c054fa1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ML Engineer- Sr Consultant</t>
+          <t>Senior Software Engineer - Java Microservices &amp; AWS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Vertex AI, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,24 +2514,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cdc87ac9c054fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff68c4379d27e34</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ETL Engineer – Cloud Data Lakehouse &amp; Pipeline Development</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hays Electrical Services</t>
+          <t>RS&amp;H</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Scala, Polars, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fca3c9a5cdbe11b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b809a99c4ae691</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer | Talent Community</t>
+          <t>Senior OCI Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6682604b8f254c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6ff336981b55a2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Microservices &amp; AWS</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff68c4379d27e34</t>
+          <t>https://www.indeed.com/viewjob?jk=54993a3d0229e1bd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RS&amp;H</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Scala, Polars, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,32 +2654,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b809a99c4ae691</t>
+          <t>https://www.indeed.com/viewjob?jk=597b472661d238bf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior OCI Consultant</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6ff336981b55a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b988244eb4ead63</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Clinical Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597b472661d238bf</t>
+          <t>https://www.indeed.com/viewjob?jk=17f0d739bf16af91</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>ML Ops Engineer I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Murphy USA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>El Dorado, AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,24 +2759,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54993a3d0229e1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>SPEC SOFTWARE DEVT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FCCI Insurance Group</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,67 +2794,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cf8e2097b223c45</t>
+          <t>https://www.indeed.com/viewjob?jk=0443de525123e0a5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Engineer-2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ELT, CI/CD</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b988244eb4ead63</t>
+          <t>https://www.indeed.com/viewjob?jk=40bc48c467a02cd0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SPEC SOFTWARE DEVT</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,32 +2864,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0443de525123e0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f8125afe117b73</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Clinical Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Talsolution</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,32 +2899,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f0d739bf16af91</t>
+          <t>https://www.indeed.com/viewjob?jk=6d10ea1903db7019</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ML Ops Engineer I</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Murphy USA</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>El Dorado, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,24 +2934,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbb1a0c9f6d5c59</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,42 +2959,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f8125afe117b73</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6937b97dd55bcf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Vertex AI, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,67 +3004,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbb1a0c9f6d5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer-2</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40bc48c467a02cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=d842e057aeca5cf9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FBS Senior Data Engineer (SnowFlake)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Talsolution</t>
+          <t>Farmers Insurance Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,32 +3074,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d10ea1903db7019</t>
+          <t>https://www.indeed.com/viewjob?jk=740eac621cae0ece</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Backend Cloud Engineer</t>
+          <t>Full Stack Engineer 4 (PySpark)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Azure, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,32 +3109,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8672fb0f9146fe17</t>
+          <t>https://www.indeed.com/viewjob?jk=5576f999a81177b2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III - ML Model Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ChenMed</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,32 +3144,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9623715fec95146</t>
+          <t>https://www.indeed.com/viewjob?jk=05e9d9a6218bf629</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Vertex AI, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,32 +3179,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0058b8ece0bab0e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,32 +3214,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d842e057aeca5cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=fce0252be99bd916</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBS Senior Data Engineer (SnowFlake)</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Farmers Insurance Group</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3249,24 +3249,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740eac621cae0ece</t>
+          <t>https://www.indeed.com/viewjob?jk=d0afa695590a0c66</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ChenMed</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e9d9a6218bf629</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e9b66a0edb57d7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Associate Data Engineer - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3319,24 +3319,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0058b8ece0bab0e</t>
+          <t>https://www.indeed.com/viewjob?jk=900e2c37f8055534</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3354,24 +3354,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce0252be99bd916</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0c66ac5431d7f0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3389,24 +3389,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0afa695590a0c66</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ee0717dbcf0c06</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - Onsite Hybrid</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3424,24 +3424,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e9b66a0edb57d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c1fe22ded8d905</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - Onsite Hybrid</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3459,24 +3459,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e2c37f8055534</t>
+          <t>https://www.indeed.com/viewjob?jk=e6429def610f5341</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Production Bioinformatics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3484,34 +3484,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0c66ac5431d7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1c2a1b4ab40cf7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Reporting</t>
+          <t>Production Bioinformatics Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JustPark</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3519,42 +3519,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, GCP, BigQuery, Data Modeling, ELT, dbt</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9067ce361a1da61</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2795ba2ac2c023</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3564,24 +3564,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6429def610f5341</t>
+          <t>https://www.indeed.com/viewjob?jk=d39184c61f9a086c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3599,24 +3599,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=79f48860ff6de64c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3634,24 +3634,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d39184c61f9a086c</t>
+          <t>https://www.indeed.com/viewjob?jk=22ff23a516389c02</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Senior Analytics Engineer (Data Platform &amp; AI Enablement)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f48860ff6de64c</t>
+          <t>https://www.indeed.com/viewjob?jk=c028808e0e50f38b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering &amp; BI/Analytics</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Advancio</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Downey, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3694,34 +3694,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ff23a516389c02</t>
+          <t>https://www.indeed.com/viewjob?jk=30859e3f8aec8e8c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Platform &amp; AI Enablement)</t>
+          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3739,24 +3739,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c028808e0e50f38b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; BI/Analytics</t>
+          <t>Senior Backend Developer (AI, Python)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Advancio</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Downey, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30859e3f8aec8e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Full-Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Abacus Technology</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3834,34 +3834,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Data Modeling, ELT, MLflow, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b862a52465289faa</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d8b03546e93eeb</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Full-Stack Developer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Abacus Technology</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Data Modeling, ELT, MLflow, Azure DevOps, Git</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3879,24 +3879,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d8b03546e93eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=35a87a481b03a8f0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3904,34 +3904,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, AKS</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35397f2df8eceb18</t>
+          <t>https://www.indeed.com/viewjob?jk=b862a52465289faa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3949,32 +3949,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a87a481b03a8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=35397f2df8eceb18</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Junior Azure Data Engineer - UniFirst</t>
+          <t>Full Stack Engineer 4 (Java, AWS)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3984,32 +3984,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44239a8e09ed622</t>
+          <t>https://www.indeed.com/viewjob?jk=464c9249b43d0e07</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IT Data Engineer II</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GCI</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4019,32 +4019,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f42d08c79858e06</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ced4fe47a4f1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Junior Azure Data Engineer - UniFirst</t>
+          <t>Full Stack Engineer 4 (Global Payment Network)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4054,32 +4054,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ec3bf6a35a904c</t>
+          <t>https://www.indeed.com/viewjob?jk=1979d7025fe17b0e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Specialist, Manufacturing Data Engineering &amp; Digital Integration</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4089,24 +4089,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082180c5e373ebfd</t>
+          <t>https://www.indeed.com/viewjob?jk=e63f85728fde97d3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Junior Azure Data Engineer - UniFirst</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4124,24 +4124,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d75297369fa64ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c44239a8e09ed622</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer – Azure</t>
+          <t>IT Data Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Symphony Enterprises Llc</t>
+          <t>GCI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4159,24 +4159,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b8c1c6cf55d819e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f42d08c79858e06</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI and Software Solutions Architect (Remote, Contract)</t>
+          <t>Senior Specialist, Manufacturing Data Engineering &amp; Digital Integration</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>INFUSE</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4194,24 +4194,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bfa1f3245af737</t>
+          <t>https://www.indeed.com/viewjob?jk=082180c5e373ebfd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Power BI / SQL Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Data Element</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4229,24 +4229,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e924fcba2ecc0fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8d75297369fa64ca</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Junior Azure Data Engineer - UniFirst</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4264,24 +4264,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
+          <t>https://www.indeed.com/viewjob?jk=24ec3bf6a35a904c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer – Azure</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>Symphony Enterprises Llc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4289,15 +4289,190 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b8c1c6cf55d819e</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Power BI / SQL Developer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>The Data Element</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e924fcba2ecc0fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Flexera</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>AWS, Athena, Step Functions, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=baa8123cd97b3b0d</t>
         </is>

--- a/results/job_matches_2026-10-02.xlsx
+++ b/results/job_matches_2026-10-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,112 +491,112 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Lakehouse Data Engineer- GrantSolutions experienced only</t>
+          <t>Senior Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>VedaPointe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Redshift, Step Functions, RDS, Azure, Spark, Scala, Spark Streaming, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16509765dca147b7</t>
+          <t>https://www.indeed.com/viewjob?jk=393b88fa8c0cfa99</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shelton - Data Engineering - Engr- Data II</t>
+          <t>AI Enterprise Architect-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ef615c91382283</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f935ebfaf4a8e1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financial Services Technology Consulting, Financial Risk Technology (FRT) Engineering - Senior</t>
+          <t>Data Solutions Architect (Financial Services)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Event Hubs, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d4e445d09c33470</t>
+          <t>https://www.indeed.com/viewjob?jk=f69508452f9349a4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -606,15 +606,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24dadced559e6fd5</t>
+          <t>https://www.indeed.com/viewjob?jk=712c0b25aa3285b3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect - Associate</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>West Valley City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,67 +659,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8052dec6a7c72b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=370116783b30ec82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect-3</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f935ebfaf4a8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08e1ab394481f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,24 +729,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712c0b25aa3285b3</t>
+          <t>https://www.indeed.com/viewjob?jk=05a68983fb26d208</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Promevo</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf209f051368f0a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3d2eb1b1d44236b5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,24 +799,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d212983a598443</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7ec08cb54132eb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer – Cloud &amp; Microservices</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32694f181dd53cec</t>
+          <t>https://www.indeed.com/viewjob?jk=c3dca3caa8fcea29</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370116783b30ec82</t>
+          <t>https://www.indeed.com/viewjob?jk=d25b4abde31c27c6</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08e1ab394481f7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b100a75517534d8</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a68983fb26d208</t>
+          <t>https://www.indeed.com/viewjob?jk=07dbaef7d4e6b9c5</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d2eb1b1d44236b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f2bc46540393f</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7ec08cb54132eb</t>
+          <t>https://www.indeed.com/viewjob?jk=9307d6216e415e2b</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3dca3caa8fcea29</t>
+          <t>https://www.indeed.com/viewjob?jk=9e546f6d2550b6b2</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25b4abde31c27c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9cc3a9842afff5</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b100a75517534d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d753c3c316503b</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dbaef7d4e6b9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a584ad2f7d15ff00</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f2bc46540393f</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb65440d87333c8</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9307d6216e415e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f11b515a70c088cb</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e546f6d2550b6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e6bf2001d3580b</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9cc3a9842afff5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5e5c4e23854a04</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d753c3c316503b</t>
+          <t>https://www.indeed.com/viewjob?jk=32200d4c67603056</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a584ad2f7d15ff00</t>
+          <t>https://www.indeed.com/viewjob?jk=9e7bd83f43b5bd8e</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb65440d87333c8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6a5d892b0aabd5</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11b515a70c088cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbff2b8b357f56c</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e6bf2001d3580b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b86ae33f22adc</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5e5c4e23854a04</t>
+          <t>https://www.indeed.com/viewjob?jk=722290f8547af1ca</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32200d4c67603056</t>
+          <t>https://www.indeed.com/viewjob?jk=5f098ed101bfb827</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e7bd83f43b5bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c34c424587e49ee0</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6a5d892b0aabd5</t>
+          <t>https://www.indeed.com/viewjob?jk=71f963121f68d02a</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbff2b8b357f56c</t>
+          <t>https://www.indeed.com/viewjob?jk=4854ae8a484d616d</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b86ae33f22adc</t>
+          <t>https://www.indeed.com/viewjob?jk=65206dd20456c905</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722290f8547af1ca</t>
+          <t>https://www.indeed.com/viewjob?jk=88b74e153a8fefec</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f098ed101bfb827</t>
+          <t>https://www.indeed.com/viewjob?jk=02838770465f88cb</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34c424587e49ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=77cd65e0f3142719</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f963121f68d02a</t>
+          <t>https://www.indeed.com/viewjob?jk=a12237447e502074</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4854ae8a484d616d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f15fa276e024e09</t>
         </is>
       </c>
     </row>
@@ -1884,32 +1884,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65206dd20456c905</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c916f7f491c0fd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,32 +1919,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b74e153a8fefec</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2c17b6e6619517</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Spark, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02838770465f88cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b838b29c7c8ad8f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer (Contract-To-Hire) (Remote)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>RelMap Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cd65e0f3142719</t>
+          <t>https://www.indeed.com/viewjob?jk=f168390c3d4033ba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,32 +2024,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12237447e502074</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c381b09f7b36b3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f15fa276e024e09</t>
+          <t>https://www.indeed.com/viewjob?jk=f13d4667a77f2594</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c916f7f491c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a7337e87916fb1c2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-To-Hire) (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RelMap Consulting</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,32 +2129,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f168390c3d4033ba</t>
+          <t>https://www.indeed.com/viewjob?jk=45753ce4c6ce5c87</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Engineer- Sr Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Databricks, Vertex AI, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2c17b6e6619517</t>
+          <t>https://www.indeed.com/viewjob?jk=1cdc87ac9c054fa1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>ETL Engineer – Cloud Data Lakehouse &amp; Pipeline Development</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Hays Electrical Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,32 +2199,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b838b29c7c8ad8f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fca3c9a5cdbe11b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer | Talent Community</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,32 +2234,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c381b09f7b36b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6682604b8f254c7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Java Microservices &amp; AWS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f13d4667a77f2594</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff68c4379d27e34</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>RS&amp;H</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Scala, Polars, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,19 +2304,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7337e87916fb1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b809a99c4ae691</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>.NET API Solutions Architect on W2</t>
+          <t>Senior OCI Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1014dc90e0bbcda2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c6ff336981b55a2</t>
         </is>
       </c>
     </row>
@@ -2351,55 +2351,55 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45753ce4c6ce5c87</t>
+          <t>https://www.indeed.com/viewjob?jk=355669dc3f76e4ef</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ETL Engineer – Cloud Data Lakehouse &amp; Pipeline Development</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hays Electrical Services</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,67 +2409,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fca3c9a5cdbe11b</t>
+          <t>https://www.indeed.com/viewjob?jk=597b472661d238bf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer | Talent Community</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6682604b8f254c7</t>
+          <t>https://www.indeed.com/viewjob?jk=2c73622306892de8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ML Engineer- Sr Consultant</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Vertex AI, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,67 +2479,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cdc87ac9c054fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b988244eb4ead63</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Microservices &amp; AWS</t>
+          <t>Senior Database and Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Scala, Databricks Lakehouse, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff68c4379d27e34</t>
+          <t>https://www.indeed.com/viewjob?jk=179abbf1882c12d5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>ML Ops Engineer I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RS&amp;H</t>
+          <t>Murphy USA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Dorado, AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Scala, Polars, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b809a99c4ae691</t>
+          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior OCI Consultant</t>
+          <t>SPEC SOFTWARE DEVT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,102 +2584,102 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6ff336981b55a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0443de525123e0a5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, PostgreSQL, Azure Cosmos DB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54993a3d0229e1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=33242063b9c39c59</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597b472661d238bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6937b97dd55bcf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ELT, CI/CD</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,67 +2689,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b988244eb4ead63</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f8125afe117b73</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Clinical Data Engineer</t>
+          <t>Data Engineer-2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f0d739bf16af91</t>
+          <t>https://www.indeed.com/viewjob?jk=40bc48c467a02cd0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ML Ops Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Murphy USA</t>
+          <t>Talsolution</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>El Dorado, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,32 +2759,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d10ea1903db7019</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SPEC SOFTWARE DEVT</t>
+          <t>Senior Backend Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Azure, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,67 +2794,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0443de525123e0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8672fb0f9146fe17</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer-2</t>
+          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Vertex AI, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40bc48c467a02cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,129 +2864,129 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f8125afe117b73</t>
+          <t>https://www.indeed.com/viewjob?jk=d842e057aeca5cf9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Workday Solution Architect - Healthcare Domain</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Talsolution</t>
+          <t>ITiNovate</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d10ea1903db7019</t>
+          <t>https://www.indeed.com/viewjob?jk=c679d851f8a17b0f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbb1a0c9f6d5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=8e725f6b9e8655bb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>FBS Senior Data Engineer (SnowFlake)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Farmers Insurance Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6937b97dd55bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=740eac621cae0ece</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,34 +2994,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Vertex AI, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Dataflow, Scala, MySQL, MongoDB, NoSQL, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=70b4420dcaff12b4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3029,34 +3029,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Dataflow, Scala, MySQL, MongoDB, NoSQL, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d842e057aeca5cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=362d82fc3d6edc44</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBS Senior Data Engineer (SnowFlake)</t>
+          <t>Full Stack Engineer 4 (PySpark)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Farmers Insurance Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,32 +3074,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740eac621cae0ece</t>
+          <t>https://www.indeed.com/viewjob?jk=5576f999a81177b2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (PySpark)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ChenMed</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,24 +3109,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5576f999a81177b2</t>
+          <t>https://www.indeed.com/viewjob?jk=05e9d9a6218bf629</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ChenMed</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e9d9a6218bf629</t>
+          <t>https://www.indeed.com/viewjob?jk=a0058b8ece0bab0e</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0058b8ece0bab0e</t>
+          <t>https://www.indeed.com/viewjob?jk=fce0252be99bd916</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce0252be99bd916</t>
+          <t>https://www.indeed.com/viewjob?jk=d0afa695590a0c66</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3249,24 +3249,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0afa695590a0c66</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ee0717dbcf0c06</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - Onsite Hybrid</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e9b66a0edb57d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c1fe22ded8d905</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - Onsite Hybrid</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3319,24 +3319,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=900e2c37f8055534</t>
+          <t>https://www.indeed.com/viewjob?jk=e6429def610f5341</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Production Bioinformatics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3344,34 +3344,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, SQL Server, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0c66ac5431d7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1c2a1b4ab40cf7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Production Bioinformatics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3379,42 +3379,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ee0717dbcf0c06</t>
+          <t>https://www.indeed.com/viewjob?jk=4e2795ba2ac2c023</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3424,129 +3424,129 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c1fe22ded8d905</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Cloud &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bunzl</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6429def610f5341</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3c303d5cb3d5a0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Production Bioinformatics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1c2a1b4ab40cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=d39184c61f9a086c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Production Bioinformatics Engineer</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2795ba2ac2c023</t>
+          <t>https://www.indeed.com/viewjob?jk=79f48860ff6de64c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3564,24 +3564,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d39184c61f9a086c</t>
+          <t>https://www.indeed.com/viewjob?jk=22ff23a516389c02</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Data Engineering &amp; BI/Analytics</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Advancio</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Downey, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3589,34 +3589,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f48860ff6de64c</t>
+          <t>https://www.indeed.com/viewjob?jk=30859e3f8aec8e8c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Developer (AI, Python)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3624,34 +3624,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ff23a516389c02</t>
+          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Platform &amp; AI Enablement)</t>
+          <t>AI Full-Stack Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Abacus Technology</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Scala, Dimensional Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Data Modeling, ELT, MLflow, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3669,24 +3669,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c028808e0e50f38b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d8b03546e93eeb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; BI/Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Advancio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Downey, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3694,34 +3694,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30859e3f8aec8e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=b862a52465289faa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
+          <t>Qualys Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>PERMEATE LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3729,34 +3729,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=202d9f3888b50c8a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Backend Developer (AI, Python)</t>
+          <t>Full Stack Engineer 4 (Java, AWS)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3764,34 +3764,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
+          <t>https://www.indeed.com/viewjob?jk=464c9249b43d0e07</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Department of Motor Vehicles California</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, ETL, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3809,24 +3809,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd56cb6c6641f35</t>
+          <t>https://www.indeed.com/viewjob?jk=5886ced4fe47a4f1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Full-Stack Developer</t>
+          <t>Full Stack Engineer 4 (Global Payment Network)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Abacus Technology</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Data Modeling, ELT, MLflow, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3844,19 +3844,19 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d8b03546e93eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=1979d7025fe17b0e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3879,67 +3879,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a87a481b03a8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e63f85728fde97d3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Azure Data Engineer - UniFirst</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b862a52465289faa</t>
+          <t>https://www.indeed.com/viewjob?jk=c44239a8e09ed622</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IT Data Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>GCI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker, AKS</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3949,32 +3949,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35397f2df8eceb18</t>
+          <t>https://www.indeed.com/viewjob?jk=8f42d08c79858e06</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Java, AWS)</t>
+          <t>Junior Azure Data Engineer - Hybrid Role</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3984,32 +3984,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464c9249b43d0e07</t>
+          <t>https://www.indeed.com/viewjob?jk=24ec3bf6a35a904c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Specialist, Manufacturing Data Engineering &amp; Digital Integration</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4019,32 +4019,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ced4fe47a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=082180c5e373ebfd</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Global Payment Network)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4054,32 +4054,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1979d7025fe17b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d75297369fa64ca</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer – Azure</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Symphony Enterprises Llc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4089,24 +4089,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63f85728fde97d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1b8c1c6cf55d819e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Junior Azure Data Engineer - UniFirst</t>
+          <t>Data Engineer Stf - E4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4114,34 +4114,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44239a8e09ed622</t>
+          <t>https://www.indeed.com/viewjob?jk=5d07b7c7063ad320</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IT Data Engineer II</t>
+          <t>Senior Power BI / SQL Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GCI</t>
+          <t>The Data Element</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4159,24 +4159,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f42d08c79858e06</t>
+          <t>https://www.indeed.com/viewjob?jk=9e924fcba2ecc0fc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Specialist, Manufacturing Data Engineering &amp; Digital Integration</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4194,24 +4194,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082180c5e373ebfd</t>
+          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4229,24 +4229,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d75297369fa64ca</t>
+          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Junior Azure Data Engineer - UniFirst</t>
+          <t>Software Engineer - Level 2 - Mobility</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4254,34 +4254,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ec3bf6a35a904c</t>
+          <t>https://www.indeed.com/viewjob?jk=4236b2cd8b3fe758</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer – Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Symphony Enterprises Llc</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Athena, Step Functions, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4298,181 +4298,6 @@
         </is>
       </c>
       <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b8c1c6cf55d819e</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Power BI / SQL Developer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>The Data Element</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e924fcba2ecc0fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Sr. Business Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7689efbfa17324</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Flexera</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Athena, Step Functions, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=baa8123cd97b3b0d</t>
         </is>

--- a/results/job_matches_2026-10-02.xlsx
+++ b/results/job_matches_2026-10-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,47 +456,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer (Data Quality &amp; Data Governance)</t>
+          <t>Senior Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>VedaPointe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Redshift, Step Functions, RDS, Azure, Spark, Scala, Spark Streaming, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d0e854dcd2654c</t>
+          <t>https://www.indeed.com/viewjob?jk=393b88fa8c0cfa99</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Pipeline Engineer</t>
+          <t>Data Solutions Architect (Financial Services)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VedaPointe</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,11 +505,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, RDS, Azure, Spark, Scala, Spark Streaming, Kafka, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,67 +519,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393b88fa8c0cfa99</t>
+          <t>https://www.indeed.com/viewjob?jk=f69508452f9349a4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect-3</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f935ebfaf4a8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=712c0b25aa3285b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Solutions Architect (Financial Services)</t>
+          <t>Managing Consultant, Palantir Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, HDFS, Spark</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69508452f9349a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4c403fce849834db</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712c0b25aa3285b3</t>
+          <t>https://www.indeed.com/viewjob?jk=370116783b30ec82</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370116783b30ec82</t>
+          <t>https://www.indeed.com/viewjob?jk=0a08e1ab394481f7</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a08e1ab394481f7</t>
+          <t>https://www.indeed.com/viewjob?jk=05a68983fb26d208</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a68983fb26d208</t>
+          <t>https://www.indeed.com/viewjob?jk=3d2eb1b1d44236b5</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d2eb1b1d44236b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7ec08cb54132eb</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7ec08cb54132eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3dca3caa8fcea29</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3dca3caa8fcea29</t>
+          <t>https://www.indeed.com/viewjob?jk=d25b4abde31c27c6</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25b4abde31c27c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b100a75517534d8</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b100a75517534d8</t>
+          <t>https://www.indeed.com/viewjob?jk=07dbaef7d4e6b9c5</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07dbaef7d4e6b9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a45f2bc46540393f</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a45f2bc46540393f</t>
+          <t>https://www.indeed.com/viewjob?jk=9307d6216e415e2b</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9307d6216e415e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e546f6d2550b6b2</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e546f6d2550b6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9cc3a9842afff5</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9cc3a9842afff5</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d753c3c316503b</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d753c3c316503b</t>
+          <t>https://www.indeed.com/viewjob?jk=a584ad2f7d15ff00</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a584ad2f7d15ff00</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb65440d87333c8</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb65440d87333c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f11b515a70c088cb</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11b515a70c088cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2e6bf2001d3580b</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e6bf2001d3580b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5e5c4e23854a04</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5e5c4e23854a04</t>
+          <t>https://www.indeed.com/viewjob?jk=32200d4c67603056</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32200d4c67603056</t>
+          <t>https://www.indeed.com/viewjob?jk=9e7bd83f43b5bd8e</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e7bd83f43b5bd8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6a5d892b0aabd5</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6a5d892b0aabd5</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbff2b8b357f56c</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbff2b8b357f56c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b86ae33f22adc</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b86ae33f22adc</t>
+          <t>https://www.indeed.com/viewjob?jk=722290f8547af1ca</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722290f8547af1ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5f098ed101bfb827</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f098ed101bfb827</t>
+          <t>https://www.indeed.com/viewjob?jk=c34c424587e49ee0</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34c424587e49ee0</t>
+          <t>https://www.indeed.com/viewjob?jk=71f963121f68d02a</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f963121f68d02a</t>
+          <t>https://www.indeed.com/viewjob?jk=4854ae8a484d616d</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4854ae8a484d616d</t>
+          <t>https://www.indeed.com/viewjob?jk=65206dd20456c905</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65206dd20456c905</t>
+          <t>https://www.indeed.com/viewjob?jk=88b74e153a8fefec</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b74e153a8fefec</t>
+          <t>https://www.indeed.com/viewjob?jk=02838770465f88cb</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02838770465f88cb</t>
+          <t>https://www.indeed.com/viewjob?jk=77cd65e0f3142719</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cd65e0f3142719</t>
+          <t>https://www.indeed.com/viewjob?jk=a12237447e502074</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12237447e502074</t>
+          <t>https://www.indeed.com/viewjob?jk=2f15fa276e024e09</t>
         </is>
       </c>
     </row>
@@ -1849,32 +1849,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f15fa276e024e09</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c916f7f491c0fd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Context Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jupiter, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,67 +1884,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c916f7f491c0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2977ae9b1f2b1c97</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Databricks Migration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2c17b6e6619517</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd5a045970f362d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, RDS, Spark, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b838b29c7c8ad8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c381b09f7b36b3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-To-Hire) (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RelMap Consulting</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,24 +1989,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f168390c3d4033ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f13d4667a77f2594</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c381b09f7b36b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a7337e87916fb1c2</t>
         </is>
       </c>
     </row>
@@ -2036,20 +2036,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f13d4667a77f2594</t>
+          <t>https://www.indeed.com/viewjob?jk=45753ce4c6ce5c87</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Engineer – Cloud Data Lakehouse &amp; Pipeline Development</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Hays Electrical Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7337e87916fb1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fca3c9a5cdbe11b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer | Talent Community</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45753ce4c6ce5c87</t>
+          <t>https://www.indeed.com/viewjob?jk=b6682604b8f254c7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ML Engineer- Sr Consultant</t>
+          <t>Senior Software Engineer - Java Microservices &amp; AWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Vertex AI, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, EMR, Athena, S3, RDS, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cdc87ac9c054fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff68c4379d27e34</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ETL Engineer – Cloud Data Lakehouse &amp; Pipeline Development</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hays Electrical Services</t>
+          <t>RS&amp;H</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Scala, Polars, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,102 +2199,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fca3c9a5cdbe11b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b809a99c4ae691</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer | Talent Community</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6682604b8f254c7</t>
+          <t>https://www.indeed.com/viewjob?jk=378fe0400293a18c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Microservices &amp; AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff68c4379d27e34</t>
+          <t>https://www.indeed.com/viewjob?jk=355669dc3f76e4ef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RS&amp;H</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Scala, Polars, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,59 +2304,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b809a99c4ae691</t>
+          <t>https://www.indeed.com/viewjob?jk=597b472661d238bf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior OCI Consultant</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c6ff336981b55a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2c73622306892de8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,34 +2364,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355669dc3f76e4ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3b988244eb4ead63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Database and Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Builders</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,34 +2399,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Scala, Databricks Lakehouse, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597b472661d238bf</t>
+          <t>https://www.indeed.com/viewjob?jk=179abbf1882c12d5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Engineer II - Zelle</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Inn-Flow Inc.</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Dimensional Modeling, Kimball, ELT</t>
+          <t>AWS, S3, RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,67 +2444,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c73622306892de8</t>
+          <t>https://www.indeed.com/viewjob?jk=2de6c389d68d3fd0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b988244eb4ead63</t>
+          <t>https://www.indeed.com/viewjob?jk=33242063b9c39c59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Database and Platform Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Builders</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Scala, Databricks Lakehouse, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,32 +2514,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179abbf1882c12d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6937b97dd55bcf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ML Ops Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Murphy USA</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>El Dorado, AR, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,59 +2549,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13256dd402d6bbc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f8125afe117b73</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SPEC SOFTWARE DEVT</t>
+          <t>Senior Data Engineer - Indiana</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0443de525123e0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=580c86eee0ba70b4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer-2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33242063b9c39c59</t>
+          <t>https://www.indeed.com/viewjob?jk=40bc48c467a02cd0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,34 +2644,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6937b97dd55bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4788a8d5c641974d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Backend Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Azure, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f8125afe117b73</t>
+          <t>https://www.indeed.com/viewjob?jk=8672fb0f9146fe17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer-2</t>
+          <t>Cloud Engineer-API -Global Industrial</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,67 +2724,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40bc48c467a02cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=8e80d57311917aaf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CX Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Talsolution</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Spark, Scala, Kafka, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d10ea1903db7019</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c2fd229b2485eb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Backend Cloud Engineer</t>
+          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, RDS, Azure, Scala, Kafka, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Vertex AI, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8672fb0f9146fe17</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (AWS), AI Infrastructure - Evinova</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Vertex AI, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,24 +2829,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc9132b08227ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=d842e057aeca5cf9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer 2</t>
+          <t>Workday Solution Architect - Healthcare Domain</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>ITiNovate</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d842e057aeca5cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=c679d851f8a17b0f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Workday Solution Architect - Healthcare Domain</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ITiNovate</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,24 +2899,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c679d851f8a17b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e725f6b9e8655bb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>FBS Senior Data Engineer (SnowFlake)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Farmers Insurance Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,34 +2924,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e725f6b9e8655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=740eac621cae0ece</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBS Senior Data Engineer (SnowFlake)</t>
+          <t>Site Reliability Engineer - ED&amp;A - Global Industrial</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Farmers Insurance Group</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,217 +2959,217 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>IAM, RDS, Azure, BigQuery, Cloud Storage, Scala, Power BI, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740eac621cae0ece</t>
+          <t>https://www.indeed.com/viewjob?jk=a687a0075d547d5c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Dataflow, Scala, MySQL, MongoDB, NoSQL, ELT, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Athena, RDS, Azure, Data Factory, Snowflake, SQL Server, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b4420dcaff12b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa8113d5aa47de0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>ChenMed</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Dataflow, Scala, MySQL, MongoDB, NoSQL, ELT, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362d82fc3d6edc44</t>
+          <t>https://www.indeed.com/viewjob?jk=05e9d9a6218bf629</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (PySpark)</t>
+          <t>Data Analytics Specialist Sr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lutz, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Cloud Storage, Snowflake, ETL, Power BI, AKS, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5576f999a81177b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6d56b5bcf4b7f491</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ChenMed</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e9d9a6218bf629</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cc391e05fe7617</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0058b8ece0bab0e</t>
+          <t>https://www.indeed.com/viewjob?jk=36d95a91a9b838e2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,32 +3179,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce0252be99bd916</t>
+          <t>https://www.indeed.com/viewjob?jk=d39184c61f9a086c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Software Engineering III - AWS, GCP, Terraform</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,32 +3214,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0afa695590a0c66</t>
+          <t>https://www.indeed.com/viewjob?jk=79f48860ff6de64c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3249,164 +3249,164 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ee0717dbcf0c06</t>
+          <t>https://www.indeed.com/viewjob?jk=22ff23a516389c02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineering &amp; BI/Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Advancio</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Downey, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c1fe22ded8d905</t>
+          <t>https://www.indeed.com/viewjob?jk=30859e3f8aec8e8c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Architect - Indiana</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6429def610f5341</t>
+          <t>https://www.indeed.com/viewjob?jk=9963d3eedaca5e2d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Production Bioinformatics Engineer</t>
+          <t>Senior Backend Developer (AI, Python)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>RDS, Azure, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1c2a1b4ab40cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Production Bioinformatics Engineer</t>
+          <t>Senior Software Engineer - Application Development</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions, Docker, Git</t>
+          <t>AWS, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e2795ba2ac2c023</t>
+          <t>https://www.indeed.com/viewjob?jk=d60692df11bdfda4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer: PDLC (Hybrid, Seattle)</t>
+          <t>Senior QA Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>ONENERGY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3414,34 +3414,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9f4efced11f6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=69b5c19120976885</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bunzl</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3459,24 +3459,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3c303d5cb3d5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b862a52465289faa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>AI Full-Stack Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Abacus Technology</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Data Modeling, ELT, MLflow, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3494,67 +3494,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d39184c61f9a086c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d8b03546e93eeb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineering III - AWS, GCP, Terraform</t>
+          <t>Senior Full-Stack Qlik Sense Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, Hive, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f48860ff6de64c</t>
+          <t>https://www.indeed.com/viewjob?jk=84a405ff1d454ffa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Azure Data Engineer - UniFirst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3564,67 +3564,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ff23a516389c02</t>
+          <t>https://www.indeed.com/viewjob?jk=c44239a8e09ed622</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; BI/Analytics</t>
+          <t>IT Data Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Advancio</t>
+          <t>GCI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Downey, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, Data Modeling, ETL, Power BI, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30859e3f8aec8e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f42d08c79858e06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Backend Developer (AI, Python)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Trisura</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3634,67 +3634,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9542b5c0a62999f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb367a6965b10d25</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Full-Stack Developer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Abacus Technology</t>
+          <t>Trisura Guarantee Insurance Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Data Modeling, ELT, MLflow, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d8b03546e93eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=b91959ca412b5c96</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Kubernetes Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>API Gateway, RDS, Vertex AI, Scala, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3704,199 +3704,199 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b862a52465289faa</t>
+          <t>https://www.indeed.com/viewjob?jk=5de56e58a17ea8ab</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Qualys Engineer</t>
+          <t>Senior Specialist, Manufacturing Data Engineering &amp; Digital Integration</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PERMEATE LLC</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202d9f3888b50c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=082180c5e373ebfd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Java, AWS)</t>
+          <t>Data Engineer Stf - E4</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=464c9249b43d0e07</t>
+          <t>https://www.indeed.com/viewjob?jk=5d07b7c7063ad320</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>​​Sr. Business Intelligence Developer​</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>KLDiscovery</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, REST API integration, Power BI, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5886ced4fe47a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e982a157a7d0ccb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (Global Payment Network)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1979d7025fe17b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f5b97a41606b41</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Software Engineer - Level 2 - Mobility</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63f85728fde97d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4236b2cd8b3fe758</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Junior Azure Data Engineer - UniFirst</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3914,24 +3914,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44239a8e09ed622</t>
+          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IT Data Engineer II</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GCI</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3949,24 +3949,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f42d08c79858e06</t>
+          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Junior Azure Data Engineer - Hybrid Role</t>
+          <t>Junior Data and AI-ML Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3974,332 +3974,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, Databricks, Spark, Scala, ETL, ELT, dbt, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ec3bf6a35a904c</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Specialist, Manufacturing Data Engineering &amp; Digital Integration</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Merck</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=082180c5e373ebfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d75297369fa64ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Data Engineer – Azure</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Symphony Enterprises Llc</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b8c1c6cf55d819e</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Engineer Stf - E4</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Stratford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d07b7c7063ad320</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Power BI / SQL Developer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>The Data Element</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e924fcba2ecc0fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32cddfff9e812a7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=387517c4b6923e55</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Software Engineer - Level 2 - Mobility</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Cintas</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Mason, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4236b2cd8b3fe758</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Flexera</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Athena, Step Functions, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, Terraform</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=baa8123cd97b3b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=29f22521f3c1e203</t>
         </is>
       </c>
     </row>
